--- a/Projeto_Operacional.xlsx
+++ b/Projeto_Operacional.xlsx
@@ -108,10 +108,13 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,9 +122,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -488,654 +488,703 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="10" max="10"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>usuario</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>senha</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>produto</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>empresa</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>toneladas_vagao</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>toneladas_caminhao</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>quantidade_vagoes</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>terminal</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>quantidade_caminhoes</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>quantidade_total</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>erick</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>@bal</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Acucar</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>LDC/Suisse</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="5" t="n">
         <v>2177</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="5" t="n">
         <v>6598</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="5" t="n">
         <v>8775</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>thiago</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>vida2708</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Acucar</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>LDC/Brasil</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="5" t="n">
         <v>1094</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>paulo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>@bal</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Acucar</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Raizen</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="5" t="n">
         <v>1400</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="5" t="n">
         <v>3600</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>emilio</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>@bal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Milho</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>CARGIL</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="5" t="n">
         <v>6566</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="5" t="n">
         <v>26566</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>rogerio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>@bal</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2025-01-11</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Milho</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>LDC/Suisse</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>20000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="5" t="n">
         <v>51515</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="5" t="n">
         <v>71515</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>saulo</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>@bal</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2025-01-25</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>CARGIL/TERCEIROS</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="5" t="n">
         <v>21515</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="5" t="n">
         <v>23515</v>
       </c>
     </row>
-    <row r="8">
-      <c r="C8" t="inlineStr">
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>gui</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>@bal</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Milho</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Raizen</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="5" t="n">
         <v>4000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Acucar</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Raizen</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="5" t="n">
         <v>-100</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Saida</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="5" t="n">
         <v>3600</v>
       </c>
     </row>
-    <row r="10">
-      <c r="C10" t="inlineStr">
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>CARGIL</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="5" t="n">
         <v>6885000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="5" t="n">
         <v>4500000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="5" t="n">
         <v>11385000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Acucar</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Raizen</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="5" t="n">
         <v>3600</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>QTDE</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>FERROVIA</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HORA</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>dataHora</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>produto</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>ferrovia</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>empresa</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="G2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2025-03-25T20:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Milho</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Rumo</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>LDC Terceiros</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1190,134 +1239,138 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>dataHora</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>ramal</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ferrovia</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>terminal</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2025-03-25T20:34</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>vli</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2025-04-04T20:34</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>mrs</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>teg</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2025-03-26T07:51</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>vli</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>teag</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1327,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,52 +1438,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teg</t>
+          <t>teag</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50000.0</t>
-        </is>
+      <c r="G2" t="n">
+        <v>1900</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>soja</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="I2" t="n">
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-02-25T00:49</t>
+          <t>2025-04-10T22:45</t>
         </is>
       </c>
     </row>
@@ -1440,47 +1485,75 @@
           <t>teg</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2000000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>soja</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2025-02-25T00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>teg</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>soja</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>2025-04-05T16:08</t>
         </is>
@@ -1655,7 +1728,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sem Operar</t>
+          <t>Operando</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
